--- a/スケジュール仮.xlsx
+++ b/スケジュール仮.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A09CB6E0-9D34-49D3-BE0C-81CEDBEC0886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2336D7-1BDF-4E2B-BC15-26A727132CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5565" yWindow="3525" windowWidth="21600" windowHeight="11295" xr2:uid="{55808E83-F442-4C94-B814-A89C9B0ED961}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55808E83-F442-4C94-B814-A89C9B0ED961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>プロト</t>
     <phoneticPr fontId="1"/>
@@ -101,6 +98,69 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土</t>
+    <rPh sb="0" eb="1">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -126,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,8 +223,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -172,13 +244,163 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -201,6 +423,84 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -209,6 +509,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF9999"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -221,9 +526,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +566,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -367,7 +672,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,7 +814,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -517,53 +822,300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB54B54-D206-413F-99EE-065973F2BCAA}">
-  <dimension ref="B2:D8"/>
+  <dimension ref="B1:M14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="5" t="s">
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B4" s="29">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="8">
         <v>3</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B5" s="6" t="s">
+      <c r="E4" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F4" s="15">
         <v>5</v>
       </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="7" t="s">
+      <c r="G4" s="15">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="H4" s="16">
         <v>7</v>
       </c>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="2" t="s">
+      <c r="K4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B5" s="17">
         <v>8</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C5" s="15">
+        <v>9</v>
+      </c>
+      <c r="D5" s="15">
+        <v>10</v>
+      </c>
+      <c r="E5" s="15">
+        <v>11</v>
+      </c>
+      <c r="F5" s="15">
+        <v>12</v>
+      </c>
+      <c r="G5" s="15">
+        <v>13</v>
+      </c>
+      <c r="H5" s="16">
+        <v>14</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B6" s="17">
+        <v>15</v>
+      </c>
+      <c r="C6" s="15">
+        <v>16</v>
+      </c>
+      <c r="D6" s="15">
+        <v>17</v>
+      </c>
+      <c r="E6" s="15">
+        <v>18</v>
+      </c>
+      <c r="F6" s="15">
+        <v>19</v>
+      </c>
+      <c r="G6" s="21">
+        <v>20</v>
+      </c>
+      <c r="H6" s="30">
+        <v>21</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="19">
+        <v>22</v>
+      </c>
+      <c r="C7" s="20">
+        <v>23</v>
+      </c>
+      <c r="D7" s="20">
+        <v>24</v>
+      </c>
+      <c r="E7" s="20">
+        <v>25</v>
+      </c>
+      <c r="F7" s="20">
+        <v>26</v>
+      </c>
+      <c r="G7" s="20">
+        <v>27</v>
+      </c>
+      <c r="H7" s="31">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B10" s="18">
+        <v>1</v>
+      </c>
+      <c r="C10" s="22">
+        <v>2</v>
+      </c>
+      <c r="D10" s="22">
+        <v>3</v>
+      </c>
+      <c r="E10" s="22">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5</v>
+      </c>
+      <c r="G10" s="22">
+        <v>6</v>
+      </c>
+      <c r="H10" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B11" s="24">
+        <v>8</v>
+      </c>
+      <c r="C11" s="22">
+        <v>9</v>
+      </c>
+      <c r="D11" s="22">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25">
+        <v>11</v>
+      </c>
+      <c r="F11" s="25">
+        <v>12</v>
+      </c>
+      <c r="G11" s="25">
+        <v>13</v>
+      </c>
+      <c r="H11" s="26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B12" s="27">
+        <v>15</v>
+      </c>
+      <c r="C12" s="28">
+        <v>16</v>
+      </c>
+      <c r="D12" s="8">
+        <v>17</v>
+      </c>
+      <c r="E12" s="8">
+        <v>18</v>
+      </c>
+      <c r="F12" s="8">
+        <v>19</v>
+      </c>
+      <c r="G12" s="8">
+        <v>20</v>
+      </c>
+      <c r="H12" s="30">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B13" s="29">
+        <v>22</v>
+      </c>
+      <c r="C13" s="8">
+        <v>23</v>
+      </c>
+      <c r="D13" s="8">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8">
+        <v>25</v>
+      </c>
+      <c r="F13" s="8">
+        <v>26</v>
+      </c>
+      <c r="G13" s="8">
+        <v>27</v>
+      </c>
+      <c r="H13" s="30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="12">
+        <v>29</v>
+      </c>
+      <c r="C14" s="13">
+        <v>30</v>
+      </c>
+      <c r="D14" s="13">
+        <v>31</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/スケジュール仮.xlsx
+++ b/スケジュール仮.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2336D7-1BDF-4E2B-BC15-26A727132CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4404281A-38CB-4623-8DB4-B089A1B224DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55808E83-F442-4C94-B814-A89C9B0ED961}"/>
+    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{55808E83-F442-4C94-B814-A89C9B0ED961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -400,7 +403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -501,6 +504,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,9 +535,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -566,7 +575,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -672,7 +681,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -814,7 +823,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -944,7 +953,7 @@
       <c r="G6" s="21">
         <v>20</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="34">
         <v>21</v>
       </c>
       <c r="K6" s="7" t="s">
@@ -974,7 +983,7 @@
       <c r="G7" s="20">
         <v>27</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="35">
         <v>28</v>
       </c>
     </row>
